--- a/Horarios/Trenes/Merlo-Lobos/DomingoMerlo.xlsx
+++ b/Horarios/Trenes/Merlo-Lobos/DomingoMerlo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -618,35 +618,35 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.3798611111111111</v>
+        <v>0.4291666666666666</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.3840277777777778</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.4381944444444444</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.4</v>
+        <v>0.4465277777777778</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.4041666666666667</v>
+        <v>0.4506944444444445</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.4076388888888889</v>
+        <v>0.4541666666666667</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.4104166666666667</v>
+        <v>0.4569444444444444</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4138888888888889</v>
+        <v>0.4604166666666666</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4194444444444445</v>
+        <v>0.4659722222222222</v>
       </c>
     </row>
     <row r="5">
@@ -657,35 +657,35 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.4291666666666666</v>
+        <v>0.5305555555555556</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.5347222222222222</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.4381944444444444</v>
+        <v>0.5395833333333333</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.4465277777777778</v>
+        <v>0.5479166666666667</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.4506944444444445</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.4541666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.4569444444444444</v>
+        <v>0.5583333333333333</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.4604166666666666</v>
+        <v>0.5618055555555556</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.4659722222222222</v>
+        <v>0.5673611111111111</v>
       </c>
     </row>
     <row r="6">
@@ -696,35 +696,35 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.5305555555555556</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.6361111111111111</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.5395833333333333</v>
+        <v>0.6409722222222223</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.5479166666666667</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.6534722222222222</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6569444444444444</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.5583333333333333</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5618055555555556</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.5673611111111111</v>
+        <v>0.66875</v>
       </c>
     </row>
     <row r="7">
@@ -735,35 +735,35 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.5826388888888889</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.5868055555555556</v>
+        <v>0.7375</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5916666666666667</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6027777777777777</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6069444444444444</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6104166666666667</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.6131944444444445</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7645833333333333</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.7701388888888889</v>
       </c>
     </row>
     <row r="8">
@@ -774,35 +774,35 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.8347222222222223</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.6361111111111111</v>
+        <v>0.8388888888888889</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6409722222222223</v>
+        <v>0.84375</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.8520833333333333</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6534722222222222</v>
+        <v>0.85625</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6569444444444444</v>
+        <v>0.8597222222222223</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.8625</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.8659722222222223</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.66875</v>
+        <v>0.8715277777777778</v>
       </c>
     </row>
     <row r="9">
@@ -813,35 +813,35 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9361111111111111</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.7375</v>
+        <v>0.9402777777777778</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.9451388888888889</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.9534722222222223</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.9576388888888889</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.9611111111111111</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.9638888888888889</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.7645833333333333</v>
+        <v>0.9673611111111111</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.9729166666666667</v>
       </c>
     </row>
     <row r="10">
@@ -850,38 +850,16 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>2826</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.7854166666666667</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0.7895833333333333</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0.7944444444444444</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.8055555555555556</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0.8097222222222222</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0.8131944444444444</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0.8159722222222222</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.8194444444444444</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.825</v>
-      </c>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+      <c r="H10" s="1" t="n"/>
+      <c r="I10" s="1" t="n"/>
+      <c r="J10" s="1" t="n"/>
+      <c r="K10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -889,38 +867,16 @@
           <t>Sentido</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>2828</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0.8347222222222223</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0.8388888888888889</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0.84375</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.8520833333333333</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0.85625</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.8597222222222223</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>0.8659722222222223</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0.8715277777777778</v>
-      </c>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+      <c r="H11" s="1" t="n"/>
+      <c r="I11" s="1" t="n"/>
+      <c r="J11" s="1" t="n"/>
+      <c r="K11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -928,38 +884,16 @@
           <t>Merlo</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>0.9361111111111111</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0.9402777777777778</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0.9451388888888889</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.9534722222222223</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0.9576388888888889</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.9611111111111111</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0.9638888888888889</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0.9673611111111111</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.9729166666666667</v>
-      </c>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -967,50 +901,16 @@
           <t>Estaciones</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>0.9861111111111112</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0.9902777777777778</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0.9951388888888889</v>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>24:05</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>24:11</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>24:16</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>24:20</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>24:25</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>24:33</t>
-        </is>
-      </c>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n"/>
+      <c r="E13" s="1" t="n"/>
+      <c r="F13" s="1" t="n"/>
+      <c r="G13" s="1" t="n"/>
+      <c r="H13" s="1" t="n"/>
+      <c r="I13" s="1" t="n"/>
+      <c r="J13" s="1" t="n"/>
+      <c r="K13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1046,7 +946,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="n"/>
@@ -1078,7 +978,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46264</v>
+        <v>46299</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>

--- a/Horarios/Trenes/Merlo-Lobos/DomingoMerlo.xlsx
+++ b/Horarios/Trenes/Merlo-Lobos/DomingoMerlo.xlsx
@@ -657,35 +657,35 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.5305555555555556</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.6361111111111111</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.5395833333333333</v>
+        <v>0.6409722222222223</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.5479166666666667</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.6534722222222222</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6569444444444444</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.5583333333333333</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5618055555555556</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.5673611111111111</v>
+        <v>0.66875</v>
       </c>
     </row>
     <row r="6">
@@ -696,35 +696,35 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.6361111111111111</v>
+        <v>0.7375</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.6409722222222223</v>
+        <v>0.7423611111111111</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.7506944444444444</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.6534722222222222</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.6569444444444444</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.7611111111111111</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.7645833333333333</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.66875</v>
+        <v>0.7701388888888889</v>
       </c>
     </row>
     <row r="7">
@@ -735,35 +735,35 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8347222222222223</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.7375</v>
+        <v>0.8388888888888889</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.84375</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.8520833333333333</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.85625</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.8597222222222223</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.8625</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.7645833333333333</v>
+        <v>0.8659722222222223</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.8715277777777778</v>
       </c>
     </row>
     <row r="8">
@@ -774,35 +774,35 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.8347222222222223</v>
+        <v>0.9361111111111111</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.8388888888888889</v>
+        <v>0.9402777777777778</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.84375</v>
+        <v>0.9451388888888889</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8520833333333333</v>
+        <v>0.9534722222222223</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.85625</v>
+        <v>0.9576388888888889</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8597222222222223</v>
+        <v>0.9611111111111111</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.8625</v>
+        <v>0.9638888888888889</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.8659722222222223</v>
+        <v>0.9673611111111111</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.8715277777777778</v>
+        <v>0.9729166666666667</v>
       </c>
     </row>
     <row r="9">
@@ -811,38 +811,16 @@
           <t>Dia</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0.9361111111111111</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.9402777777777778</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.9451388888888889</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.9534722222222223</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.9576388888888889</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.9611111111111111</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9638888888888889</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0.9673611111111111</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.9729166666666667</v>
-      </c>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="n"/>
+      <c r="D9" s="1" t="n"/>
+      <c r="E9" s="1" t="n"/>
+      <c r="F9" s="1" t="n"/>
+      <c r="G9" s="1" t="n"/>
+      <c r="H9" s="1" t="n"/>
+      <c r="I9" s="1" t="n"/>
+      <c r="J9" s="1" t="n"/>
+      <c r="K9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -946,7 +924,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="n"/>

--- a/Horarios/Trenes/Merlo-Lobos/DomingoMerlo.xlsx
+++ b/Horarios/Trenes/Merlo-Lobos/DomingoMerlo.xlsx
@@ -618,35 +618,35 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.4291666666666666</v>
+        <v>0.3798611111111111</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3840277777777778</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.4381944444444444</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.4465277777777778</v>
+        <v>0.4</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.4506944444444445</v>
+        <v>0.4041666666666667</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.4541666666666667</v>
+        <v>0.4076388888888889</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.4569444444444444</v>
+        <v>0.4104166666666667</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4604166666666666</v>
+        <v>0.4138888888888889</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4659722222222222</v>
+        <v>0.4194444444444445</v>
       </c>
     </row>
     <row r="5">
@@ -657,35 +657,35 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.4291666666666666</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.6361111111111111</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6409722222222223</v>
+        <v>0.4381944444444444</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.4465277777777778</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6534722222222222</v>
+        <v>0.4506944444444445</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6569444444444444</v>
+        <v>0.4541666666666667</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.4569444444444444</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.4604166666666666</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.66875</v>
+        <v>0.4659722222222222</v>
       </c>
     </row>
     <row r="6">
@@ -696,35 +696,35 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.5305555555555556</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.7375</v>
+        <v>0.5347222222222222</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7423611111111111</v>
+        <v>0.5395833333333333</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7506944444444444</v>
+        <v>0.5479166666666667</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.7548611111111111</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.5583333333333333</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.7645833333333333</v>
+        <v>0.5618055555555556</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.5673611111111111</v>
       </c>
     </row>
     <row r="7">
@@ -735,35 +735,35 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.8347222222222223</v>
+        <v>0.5826388888888889</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.8388888888888889</v>
+        <v>0.5868055555555556</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.84375</v>
+        <v>0.5916666666666667</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8520833333333333</v>
+        <v>0.6027777777777777</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.85625</v>
+        <v>0.6069444444444444</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8597222222222223</v>
+        <v>0.6104166666666667</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.8625</v>
+        <v>0.6131944444444445</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8659722222222223</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.8715277777777778</v>
+        <v>0.6222222222222222</v>
       </c>
     </row>
     <row r="8">
@@ -774,35 +774,35 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.9361111111111111</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.9402777777777778</v>
+        <v>0.6361111111111111</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9451388888888889</v>
+        <v>0.6409722222222223</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9534722222222223</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9576388888888889</v>
+        <v>0.6534722222222222</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9611111111111111</v>
+        <v>0.6569444444444444</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9638888888888889</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.9673611111111111</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.9729166666666667</v>
+        <v>0.66875</v>
       </c>
     </row>
     <row r="9">
@@ -811,16 +811,38 @@
           <t>Dia</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n"/>
-      <c r="C9" s="1" t="n"/>
-      <c r="D9" s="1" t="n"/>
-      <c r="E9" s="1" t="n"/>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="n"/>
-      <c r="I9" s="1" t="n"/>
-      <c r="J9" s="1" t="n"/>
-      <c r="K9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.7423611111111111</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.7506944444444444</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.7548611111111111</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.7611111111111111</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.7645833333333333</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.7701388888888889</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -828,16 +850,38 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="1" t="n"/>
-      <c r="E10" s="1" t="n"/>
-      <c r="F10" s="1" t="n"/>
-      <c r="G10" s="1" t="n"/>
-      <c r="H10" s="1" t="n"/>
-      <c r="I10" s="1" t="n"/>
-      <c r="J10" s="1" t="n"/>
-      <c r="K10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0.7854166666666667</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.7895833333333333</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.7944444444444444</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.8097222222222222</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.8131944444444444</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.8159722222222222</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.8194444444444444</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.825</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -845,16 +889,38 @@
           <t>Sentido</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
-      <c r="D11" s="1" t="n"/>
-      <c r="E11" s="1" t="n"/>
-      <c r="F11" s="1" t="n"/>
-      <c r="G11" s="1" t="n"/>
-      <c r="H11" s="1" t="n"/>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="n"/>
-      <c r="K11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.8347222222222223</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.8388888888888889</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.8520833333333333</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.85625</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.8597222222222223</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.8659722222222223</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.8715277777777778</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -862,16 +928,38 @@
           <t>Merlo</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n"/>
-      <c r="C12" s="1" t="n"/>
-      <c r="D12" s="1" t="n"/>
-      <c r="E12" s="1" t="n"/>
-      <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
-      <c r="K12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.9361111111111111</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.9402777777777778</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.9451388888888889</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9534722222222223</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.9576388888888889</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.9638888888888889</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.9673611111111111</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.9729166666666667</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -879,16 +967,50 @@
           <t>Estaciones</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
-      <c r="E13" s="1" t="n"/>
-      <c r="F13" s="1" t="n"/>
-      <c r="G13" s="1" t="n"/>
-      <c r="H13" s="1" t="n"/>
-      <c r="I13" s="1" t="n"/>
-      <c r="J13" s="1" t="n"/>
-      <c r="K13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.9861111111111112</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.9902777777777778</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.9951388888888889</v>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>24:05</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>24:11</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>24:16</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>24:20</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>24:25</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>24:33</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -924,7 +1046,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="n"/>
@@ -956,7 +1078,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46299</v>
+        <v>46313</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
